--- a/immtell-webflow-pages.xlsx
+++ b/immtell-webflow-pages.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pages" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CMS Items" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pages'!$A$1:$E$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CMS Items'!$A$1:$F$238</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1929,4 +1931,7882 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F238"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="95" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Published Path</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Item ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Full URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ewen McKenzie</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>/about/ewen-mckenzie</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6aa83ac7aacfc4a904d2cf4a</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/about/ewen-mckenzie</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gavin Webster</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>/about/gavin-webster</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6aa83ab0209d3d20feeb9b40</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/about/gavin-webster</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Academic Recruitment Across Three Faculties</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>/business/case-study/academic-recruitment-three-faculties</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6a90bb376831d4d873fcd039</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/case-study/academic-recruitment-three-faculties</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A Compliance Review Before a Basic Compliance Assessment</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>/business/case-study/compliance-review-before-bca</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6a90bb376831d4d873fcd03b</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/case-study/compliance-review-before-bca</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Strengthening Sponsor Licence Compliance for a UK University</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>/business/case-study/compliance-support-for-a-universitys-international-student-programme</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6aa02540610ea1cad31b294b</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/case-study/compliance-support-for-a-universitys-international-student-programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A First Sponsor Licence for a Scaling Software Business</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>/business/case-study/first-sponsor-licence-scaling-software-business</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6a90bb376831d4d873fcd02d</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/case-study/first-sponsor-licence-scaling-software-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Supporting Overseas Healthcare Recruitment for UK Care Providers</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>/business/case-study/global-healthcare-recruitment-for-carers-and-nurses</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6aa02540610ea1cad31b294d</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/case-study/global-healthcare-recruitment-for-carers-and-nurses</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Confirming the Health and Care Route for a Nursing Programme</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>/business/case-study/health-care-route-nursing-programme</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6a90bb376831d4d873fcd035</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/case-study/health-care-route-nursing-programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A Mock Audit Before a First Home Office Visit</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>/business/case-study/mock-audit-before-first-home-office-visit</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6a90bb376831d4d873fcd031</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/case-study/mock-audit-before-first-home-office-visit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Supporting a Global Technology Company Establishing its UK Presence</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>/business/case-study/paving-the-way-for-a-global-tech-companys-expansion</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6aa02540610ea1cad31b294f</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/case-study/paving-the-way-for-a-global-tech-companys-expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Deploying Specialist Talent for a UK Nuclear Energy Project</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>/business/case-study/powering-up-a-uk-nuclear-project-by-overcoming-cross-border-workforce-challenges</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6aa02540610ea1cad31b2951</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/case-study/powering-up-a-uk-nuclear-project-by-overcoming-cross-border-workforce-challenges</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Priority CoS Allocation Against a Product Launch Deadline</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>/business/case-study/priority-cos-allocation-product-launch</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6a90bb376831d4d873fcd02f</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/case-study/priority-cos-allocation-product-launch</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Rebuilding Sponsor Duties After Key Personnel Left</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>/business/case-study/rebuilding-sponsor-duties-after-personnel-left</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6a90bb376831d4d873fcd033</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/case-study/rebuilding-sponsor-duties-after-personnel-left</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Restoring a B-Rating After a Compliance Downgrade</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>/business/case-study/restoring-b-rating-after-downgrade</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6a90bb376831d4d873fcd02b</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/case-study/restoring-b-rating-after-downgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Rebuilding Right to Work Processes Across Six Care Sites</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>/business/case-study/right-to-work-processes-six-care-sites</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6a90bb376831d4d873fcd037</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/case-study/right-to-work-processes-six-care-sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Deploying Specialist Talent for a UK Nuclear Energy Project</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>/business/case-study/specialist-talent-uk-nuclear-energy-project</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6a90bb376831d4d873fcd029</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/case-study/specialist-talent-uk-nuclear-energy-project</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sponsor Licence Application for an Independent Care Home Group</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>/business/case-study/sponsor-licence-independent-care-home-group</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6a8a026f15d5f77686dd0dce</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/case-study/sponsor-licence-independent-care-home-group</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Supporting an International Consultancy with UK Immigration Compliance</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>/business/case-study/uk-immigration-support-for-an-international-consultancy</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6aa02540610ea1cad31b2953</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/case-study/uk-immigration-support-for-an-international-consultancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Establishing a UK Office Through the Expansion Worker Route</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>/business/case-study/uk-office-expansion-worker-route</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6a90bb376831d4d873fcd03d</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/case-study/uk-office-expansion-worker-route</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Defence</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sectors</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>/business/sectors/defence</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6a94bb6cabcea4e8777645d8</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/sectors/defence</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sectors</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>/business/sectors/education</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>6a94bb6df6a5ac112f407422</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/sectors/education</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sectors</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>/business/sectors/energy</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6a94bb6ed9580ac136f8cf4e</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/sectors/energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Film &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sectors</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>/business/sectors/film-entertainment</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>6a94bb70330bcb583cc27e24</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/sectors/film-entertainment</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sectors</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>/business/sectors/financial-services</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>6a94bb71ecca377464ce8bd4</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/sectors/financial-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sectors</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>/business/sectors/fintech</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>6a94bb72abcea4e8777646a7</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/sectors/fintech</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sectors</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>/business/sectors/healthcare</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>6a94bb73b2a74cfb7f7ac881</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/sectors/healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sectors</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>/business/sectors/hospitality</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>6a94bb742845e7c9a92d880f</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/sectors/hospitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Manufacturing &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sectors</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>/business/sectors/manufacturing-engineering</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>6a94bb754c34350fb3c5b1f1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/sectors/manufacturing-engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sectors</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>/business/sectors/professional-services</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>6a94bb77f6de01d0606566f1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/sectors/professional-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sectors</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>/business/sectors/retail</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>6a94bb78c6dd4f0824d077d7</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/sectors/retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sports &amp; Athletics</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sectors</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>/business/sectors/sports-athletics</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>6a94bb79ecca377464ce8cfe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/sectors/sports-athletics</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sectors</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>/business/sectors/technology</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>6a94bb7b28a7fa4559cd166f</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/business/sectors/technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Case Study Sectors</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>/case-study-sectors/education</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>6a8a023aa7b9defbda0c3a2b</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/case-study-sectors/education</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Case Study Sectors</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>/case-study-sectors/energy</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>6a8a023aa7b9defbda0c3a23</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/case-study-sectors/energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Health and Social Care</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Case Study Sectors</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>/case-study-sectors/health-and-social-care</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>6a8a023aa7b9defbda0c3a29</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/case-study-sectors/health-and-social-care</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Case Study Sectors</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>/case-study-sectors/professional-services</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>6a8a023aa7b9defbda0c3a27</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/case-study-sectors/professional-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Case Study Sectors</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>/case-study-sectors/technology</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>6a8a023aa7b9defbda0c3a25</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/case-study-sectors/technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>How the Home Office Identifies Sponsor Compliance Risk, and Why the Landscape Has Changed</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>/events/how-the-home-office-identifies-sponsor-compliance-risk-and-why-the-landscape-has-changed</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>6a89b7b314d1a11659ab92b5</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/events/how-the-home-office-identifies-sponsor-compliance-risk-and-why-the-landscape-has-changed</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sponsor Salary &amp; Payroll Compliance: The Discrepancies That Can Put Your Licence at Risk</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>/events/sponsor-salary-payroll-compliance-the-discrepancies-that-can-put-your-licence-at-risk</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>6a89b7b314d1a11659ab92b7</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/events/sponsor-salary-payroll-compliance-the-discrepancies-that-can-put-your-licence-at-risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Australia Immigration</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>News Topics</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>/news-topics/australia-immigration</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>6a89e44cb52c25150dc6dde2</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/news-topics/australia-immigration</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Employer Sponsorship</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>News Topics</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>/news-topics/employer-sponsorship</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>6a89e44cb52c25150dc6ddd8</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/news-topics/employer-sponsorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Family &amp; Settlement</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>News Topics</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>/news-topics/family-settlement</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>6a89e44cb52c25150dc6dddc</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/news-topics/family-settlement</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>News Topics</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>/news-topics/government</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>6aa04a3f1778dc215f7cbc32</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/news-topics/government</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Immtell</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>News Topics</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>/news-topics/immtell</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>6aa04a2f5dbdf3dc6b28076b</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/news-topics/immtell</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Student Visas</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>News Topics</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>/news-topics/student-visas</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6a89e44cb52c25150dc6ddde</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/news-topics/student-visas</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Visitor Visas</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>News Topics</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>/news-topics/visitor-visas</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>6a89e44cb52c25150dc6dde0</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/news-topics/visitor-visas</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Work Visas</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>News Topics</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>/news-topics/work-visas</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>6a89e44cb52c25150dc6ddda</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/news-topics/work-visas</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Absences and Settlement: How the Limits Are Assessed</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>/resource-article/absences-and-settlement-limits</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>6a90bb027fc914e700058e78</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/absences-and-settlement-limits</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Assign CoS Before SMS Goes Down at 18:00 21 July</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>/resource-article/act-now-assign-cos-before-sms-goes-offline-at-1800-on-21-july</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>6aa04ee51b5a1fce069ce3f7</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/act-now-assign-cos-before-sms-goes-offline-at-1800-on-21-july</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Australia Working Holiday Visa Extended</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>/resource-article/australia-extends-working-holiday-visa-eligibility</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>6aa04ee51b5a1fce069ce3f9</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/australia-extends-working-holiday-visa-eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Australian Skilled Migration Changes: A UK Comparison</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>/resource-article/australian-skilled-migration-uk-comparison</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>6a90bb027fc914e700058e82</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/australian-skilled-migration-uk-comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Automatic Upgrade to EU Settled Status</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>/resource-article/automatic-settled-status-grants-for-eligible-pre-settled-status-holders</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>6aa04ee51b5a1fce069ce3fb</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/automatic-settled-status-grants-for-eligible-pre-settled-status-holders</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BRP and BRC Extension for UK Visa Holders</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>/resource-article/brp-and-brc-extension-new-deadline-for-uk-visa-holders</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>6aa04ee51b5a1fce069ce3fd</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/brp-and-brc-extension-new-deadline-for-uk-visa-holders</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Business Visitor Rules: Where the Line Sits</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>/resource-article/business-visitor-rules-where-line-sits</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>6a90bb027fc914e700058e7e</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/business-visitor-rules-where-line-sits</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Care Worker Recruitment Requirement 9 April 2025</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>/resource-article/care-worker-recruitment-requirement-from-9-april-2025</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>6aa04ee51b5a1fce069ce3ff</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/care-worker-recruitment-requirement-from-9-april-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Increase to Immigration Health Surcharge Feb 24</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>/resource-article/confirmed-increase-to-immigration-health-surcharge-ihs-on-6-february-2024</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>6aa04f3754c9dc9561e51d0d</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/confirmed-increase-to-immigration-health-surcharge-ihs-on-6-february-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Certificate of Sponsorship Allocations: What Changed This Year</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>/resource-article/cos-allocations-what-changed</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>6a90bb027fc914e700058e6e</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/cos-allocations-what-changed</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ETA Required for More Travellers to UK</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>/resource-article/eta-requirement-in-effect-for-non-european-travellers-to-the-uk</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>6aa04f3754c9dc9561e51d0f</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/eta-requirement-in-effect-for-non-european-travellers-to-the-uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Final Rollout: UK ETA Mandatory for All Visitors</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>/resource-article/final-rollout-uk-eta-mandatory-for-european-visitors-from-april-2025</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>6aa04f3754c9dc9561e51d11</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/final-rollout-uk-eta-mandatory-for-european-visitors-from-april-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Financial Requirement Evidence: What Caseworkers Expect</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>/resource-article/financial-requirement-evidence-expectations</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>6a90bb027fc914e700058e76</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/financial-requirement-evidence-expectations</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Going Rate Revisions and Roles Near the Threshold</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>/resource-article/going-rate-revisions-threshold-roles</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>6a90bb027fc914e700058e72</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/going-rate-revisions-threshold-roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Home Secretary’s Statement on Migration July 2024</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>/resource-article/home-secretarys-statement-on-migration-july-2024</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>6aa04f3754c9dc9561e51d13</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/home-secretarys-statement-on-migration-july-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2024 IHS Increase Delayed</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>/resource-article/ihs-increase-delayed</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>6aa04f3754c9dc9561e51d15</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/ihs-increase-delayed</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Increase to UK Visa Fees October 2023</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>/resource-article/imminent-changes-in-uk-skilled-worker-visa-fees-insights-for-employers</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>6aa04f79d110108eceae9856</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/imminent-changes-in-uk-skilled-worker-visa-fees-insights-for-employers</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Immtell Brighton Office</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>/resource-article/immtell-opens-new-brighton-office-to-support-sussex-based-employers-and-individuals</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>6aa04f79d110108eceae9858</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/immtell-opens-new-brighton-office-to-support-sussex-based-employers-and-individuals</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>UK Skilled Worker Visa &amp; Health Surcharge Changes</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>/resource-article/important-alert-uk-skilled-worker-visa-health-surcharge-changes</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>6aa04f79d110108eceae985a</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/important-alert-uk-skilled-worker-visa-health-surcharge-changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Key Dates for 2024 UK Immigration Changes</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>/resource-article/key-uk-immigration-dates-for-2024</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>6aa04f79d110108eceae985c</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/key-uk-immigration-dates-for-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MAC Report on Salary Thresholds Dec 2025</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>/resource-article/mac-report-on-salary-thresholds</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>6aa04f79d110108eceae985e</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/mac-report-on-salary-thresholds</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Major Reform to UK Settlement (ILR) Planned</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>/resource-article/major-reform-to-uk-settlement-ilr-planned</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>6aa04fe56f56271f36cd6247</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/major-reform-to-uk-settlement-ilr-planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>New Rules for Sponsors of Care Workers in the UK</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>/resource-article/new-guidance-for-sponsors-of-care-workers-and-senior-care-workers</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>6aa04fe56f56271f36cd6249</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/new-guidance-for-sponsors-of-care-workers-and-senior-care-workers</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Record-Keeping Duties Sponsors Most Often Miss</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>/resource-article/record-keeping-duties-sponsors-miss</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>6a90bb027fc914e700058e70</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/record-keeping-duties-sponsors-miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Sending Staff to the UK on Visitor Visas</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>/resource-article/sending-staff-uk-visitor-visas</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>6a90bb027fc914e700058e80</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/sending-staff-uk-visitor-visas</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Major Changes to UK Immigration Rules April 2024</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>/resource-article/significant-changes-to-uk-immigration-rules-from-4-april-2024</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>6aa04fe56f56271f36cd624b</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/significant-changes-to-uk-immigration-rules-from-4-april-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Skilled Worker Applications: Common Reasons for Delay</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>/resource-article/skilled-worker-common-delays</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>6a90bb027fc914e700058e74</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/skilled-worker-common-delays</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Home Office SMS Update</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>/resource-article/sponsor-management-system-update-for-skilled-worker-sponsorship</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>6aa04fe56f56271f36cd624d</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/sponsor-management-system-update-for-skilled-worker-sponsorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Student Route Compliance: What Institutions Now Report</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>/resource-article/student-route-compliance-reporting</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>6a90bb027fc914e700058e7a</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/student-route-compliance-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Switching From the Student Route After Graduation</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>/resource-article/switching-from-student-route</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>6a90bb027fc914e700058e7c</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/switching-from-student-route</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>UK Immigration White Paper 2025: Proposals &amp; Impact</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>/resource-article/the-2025-uk-immigration-white-paper-key-proposals-risks-and-what-comes-next</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>6aa04fe56f56271f36cd624f</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/the-2025-uk-immigration-white-paper-key-proposals-risks-and-what-comes-next</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Move to a UK eVisa: All You Need to Know</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>/resource-article/transition-to-uk-evisa-what-you-need-to-know</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>6aa050b7242a21ddd1634ce2</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/transition-to-uk-evisa-what-you-need-to-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>UK Immigration Changes April 2026: What Employers Need to Do Now</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>/resource-article/uk-immigration-changes-april-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>6a89e4a385e90dc2f27147f0</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/uk-immigration-changes-april-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>UK Immigration Changes April 2026: Employers Guide</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>/resource-article/uk-immigration-changes-april-2026-what-employers-need-to-do-now</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>6aa050b7242a21ddd1634ce4</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/uk-immigration-changes-april-2026-what-employers-need-to-do-now</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>UK Immigration Changes Confirmed From 22 July 2025</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>/resource-article/uk-immigration-changes-confirmed-from-22-july-2025</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>6aa050b7242a21ddd1634ce6</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/uk-immigration-changes-confirmed-from-22-july-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>UK Immigration Fees Increasing from 8 April 2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>/resource-article/uk-immigration-fees-increasing-from-8-april-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>6aa050b7242a21ddd1634ce8</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/uk-immigration-fees-increasing-from-8-april-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>UK Immigration Rule Changes – March 2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>/resource-article/uk-immigration-rule-changes--march-2026-statement-of-changes</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>6aa050b7242a21ddd1634cea</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/uk-immigration-rule-changes--march-2026-statement-of-changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>UK Immigration Rules April 2025:  Employer Update</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>/resource-article/uk-immigration-rule-changes-april-2025-key-updates-for-employers</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>6aa051935ba6168fd48beb4c</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/uk-immigration-rule-changes-april-2025-key-updates-for-employers</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>UK Immigration Rule Changes July 2025: Key Updates</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>/resource-article/uk-immigration-rule-changes-july-2025-key-updates-for-employers-and-applicants</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>6aa051935ba6168fd48beb4e</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/uk-immigration-rule-changes-july-2025-key-updates-for-employers-and-applicants</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>UK Immigration Rule Changes October 2025</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>/resource-article/uk-immigration-rule-changes-october-2025-key-updates-for-employers-and-applicants</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>6aa051935ba6168fd48beb50</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/uk-immigration-rule-changes-october-2025-key-updates-for-employers-and-applicants</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>UK Sponsor Licence Changes March 2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>/resource-article/uk-sponsor-guidance-update--new-duties-for-sponsors</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>6aa051935ba6168fd48beb52</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/uk-sponsor-guidance-update--new-duties-for-sponsors</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>UK Visa Fee Increases from 9 April 2025</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>/resource-article/uk-visa-and-sponsorship-fee-increases-from-9-april-2025</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>6aa051935ba6168fd48beb54</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/uk-visa-and-sponsorship-fee-increases-from-9-april-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>UK's Electronic Travel Authorisation (ETA) System</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>/resource-article/uks-new-electronic-travel-authorisation-eta-system</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>6aa051d10135cf70b014e257</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/uks-new-electronic-travel-authorisation-eta-system</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>UK Immigration Fee Increases 2025</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>/resource-article/upcoming-uk-immigration-fee-increases-2025</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>6aa051d10135cf70b014e259</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/upcoming-uk-immigration-fee-increases-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Sponsor Licence Holders: Renewal Process From 6 April</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>/resource-article/update-for-uk-sponsor-licence-holders-renewal-process-changes</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>6aa051d10135cf70b014e25b</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/update-for-uk-sponsor-licence-holders-renewal-process-changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>UK Immigration Statement of Changes December 2023</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>/resource-article/welcome-immigration-updates-from-the-uk-government-for-visitors</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>6aa051d10135cf70b014e25d</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-article/welcome-immigration-updates-from-the-uk-government-for-visitors</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Resource Types</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>/resource-types/download</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>6a89ad5bef9dc373580766c3</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-types/download</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Resource Types</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>/resource-types/guide</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>6a89ad5bef9dc373580766bd</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-types/guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Resource Types</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>/resource-types/video</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>6a89ad5bef9dc373580766bf</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-types/video</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Resource Types</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>/resource-types/webinar</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>6a89ad5bef9dc373580766c1</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resource-types/webinar</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>7 Common Sponsor Duties HR Teams Miss</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>/resources-pages/7-common-sponsor-duties-hr-teams-miss</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>6a99dd144c88ae31eb35a102</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/7-common-sponsor-duties-hr-teams-miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>All You Need to Know About Sponsor Licences</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>/resources-pages/all-you-need-to-know-about-sponsor-licences</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>6a99dcf383cc493fad261bec</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/all-you-need-to-know-about-sponsor-licences</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>An Honest Review of the UK Sponsor Licence Process</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>/resources-pages/an-honest-review-of-the-uk-sponsor-licence-process</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>6a99dd36a431e6b9e74b243e</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/an-honest-review-of-the-uk-sponsor-licence-process</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Avoid UK Illegal Working Penalties - Right to Work Compliance 2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>/resources-pages/avoid-uk-illegal-working-penalties-right-to-work-compliance-2025</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>6a99dd1513c970b4552e81f6</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/avoid-uk-illegal-working-penalties-right-to-work-compliance-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Become a Sponsor - Steps for Employers and Businesses</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>/resources-pages/become-a-sponsor-steps-for-employers-and-businesses</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>6a99dd085086fe328a29b783</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/become-a-sponsor-steps-for-employers-and-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Business Visas for the UK Guide</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>/resources-pages/business-visas-for-the-uk-guide</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>6a99dd1f2b6d13b7e4164f2f</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/business-visas-for-the-uk-guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Travel After Citizenship Ceremony - Before First British Passport</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>/resources-pages/can-i-travel-after-my-citizenship-ceremony-and-before-receiving-my-first-british-passport</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d49b</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/can-i-travel-after-my-citizenship-ceremony-and-before-receiving-my-first-british-passport</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Certificate of Sponsorship - A Guide For Employers</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>/resources-pages/certificate-of-sponsorship-a-guide-for-employers</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>6a99dcf458447882c7111e75</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/certificate-of-sponsorship-a-guide-for-employers</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Choose the Right UK Immigration Consultancy for Your Business</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>/resources-pages/choose-the-right-uk-immigration-consultancy-for-your-business</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>6a99dd158c23868091ce06b7</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/choose-the-right-uk-immigration-consultancy-for-your-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Common Right to Work Check Mistakes That Could Lead to Civil Penalties</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>/resources-pages/common-right-to-work-check-mistakes-that-could-lead-to-civil-penalties</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>6a99dd09b0fde4ff7a3810ac</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/common-right-to-work-check-mistakes-that-could-lead-to-civil-penalties</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Do Brighton SMEs Need a Sponsor Licence to Hire Overseas Talent</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>/resources-pages/do-brighton-smes-need-a-sponsor-licence-to-hire-overseas-talent</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>6a99dd20cdae18d80850b4be</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/do-brighton-smes-need-a-sponsor-licence-to-hire-overseas-talent</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Expertise of Immigration Law Firms for Corporations and Businesses</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>/resources-pages/expertise-of-immigration-law-firms-for-corporations-and-businesses</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>6a99dd211575f53a96c2a857</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/expertise-of-immigration-law-firms-for-corporations-and-businesses</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Family Visas - Join Your Family in the UK</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>/resources-pages/family-visas-join-your-family-in-the-uk</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>6a99dcf517c8e400a5f8f935</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/family-visas-join-your-family-in-the-uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>UK Graduate Trainee Visa (GBM)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>/resources-pages/graduate-trainee-visa-uk-global-business-mobility-visa</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>6a99dd1a8c23868091ce0809</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/graduate-trainee-visa-uk-global-business-mobility-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>7b. Guide to Documents Required for a UK Tourist Visa from India</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>/resources-pages/guide-to-documents-required-for-a-uk-tourist-visa-from-india</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>6a99dd41c801b6e75a4f1e8a</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/guide-to-documents-required-for-a-uk-tourist-visa-from-india</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Guide to England Family Visas</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>/resources-pages/guide-to-england-family-visas</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>6a99dd0a27dcf5fe2105efc6</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/guide-to-england-family-visas</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Guide to Right to Work Checks in 2026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>/resources-pages/guide-to-right-to-work-checks-in-2025</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>6a99dcf6a64961b7c41d7110</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/guide-to-right-to-work-checks-in-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Guide to Successfully Obtaining a UK Work Visa in 2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>/resources-pages/guide-to-successfully-obtaining-a-uk-work-visa-in-2025</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>6a99dd2722f3e73c9fa50349</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/guide-to-successfully-obtaining-a-uk-work-visa-in-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Home Office Contact Us</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>/resources-pages/home-office-contact-us</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d49d</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/home-office-contact-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Home Office Sponsor Licence Holders - Reporting Duties</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>/resources-pages/home-office-sponsor-licence-holders-reporting-duties</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>6a99dd0ba36cbb5c4112d780</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/home-office-sponsor-licence-holders-reporting-duties</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>How Much Do UK Business Immigration Consultants Charge</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>/resources-pages/how-much-do-uk-business-immigration-consultants-charge</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>6a99dd0b9ec6a6a97fde0eb2</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/how-much-do-uk-business-immigration-consultants-charge</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>How Much Does a UK Sponsor Licence Cost in 2026</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>/resources-pages/how-much-does-a-uk-sponsor-licence-cost-in-2025</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>6a99dd3c5086fe328a29d407</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/how-much-does-a-uk-sponsor-licence-cost-in-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>How Much Does a UK Visa Cost in 2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>/resources-pages/how-much-does-a-uk-visa-cost-in-2025</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>6a99dd22c0cf7932055cff57</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/how-much-does-a-uk-visa-cost-in-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>How to Get a Skilled Worker Visa UK</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>/resources-pages/how-to-get-a-skilled-worker-visa-uk</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>6a99dd19455dfaf3b17d7b2b</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/how-to-get-a-skilled-worker-visa-uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>How to Get a Work Visa in the UK</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>/resources-pages/how-to-get-a-work-visa-in-the-uk</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>6a99dd229ec6a6a97fde1716</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/how-to-get-a-work-visa-in-the-uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Make the Most of a Youth Mobility Visa in the UK</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>/resources-pages/how-to-make-the-most-of-a-youth-mobility-visa-in-the-uk</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d49f</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/how-to-make-the-most-of-a-youth-mobility-visa-in-the-uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>How to Respond When Your Home Office Sponsor Licence is Revoked</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>/resources-pages/how-to-respond-when-your-home-office-sponsor-licence-is-revoked</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>6a99dcf6e5004eb31acc7298</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/how-to-respond-when-your-home-office-sponsor-licence-is-revoked</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>How to Tell if Your Sponsor Licence Is at Risk</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>/resources-pages/how-to-tell-if-your-sponsor-licence-is-at-risk</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>6a99dd239f2eccd67839df0e</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/how-to-tell-if-your-sponsor-licence-is-at-risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Immigration Skills Charge - A Guide for Employers</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>/resources-pages/immigration-skills-charge-a-guide-for-employers</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>6a99dd052792032cd81d5263</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/immigration-skills-charge-a-guide-for-employers</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>In-house HR Team vs External Immigration Support</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>/resources-pages/in-house-hr-team-vs-external-immigration-support-which-is-more-cost-effective</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>6a99dcf727dcf5fe2105e52d</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/in-house-hr-team-vs-external-immigration-support-which-is-more-cost-effective</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Indefinite Leave to Remain - Settle in the UK</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>/resources-pages/indefinite-leave-to-remain-settle-in-the-uk</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>6a99dcf8112cf1afdc857cfb</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/indefinite-leave-to-remain-settle-in-the-uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Indian Carers and Nurses Seeking Work in the UK</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>/resources-pages/indian-carers-and-nurses-seeking-work-in-the-uk</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d4a1</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/indian-carers-and-nurses-seeking-work-in-the-uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Life in the UK Test - 2026 Guide</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>/resources-pages/life-in-the-uk-test-2025-guide</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>6a99dd0cf56401e81197ec9a</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/life-in-the-uk-test-2025-guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Mistakes Brighton Employers Make With Sponsor Licences</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>/resources-pages/mistakes-brighton-employers-make-with-sponsor-licences</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>6a99dd02b3e9c79895ea369e</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/mistakes-brighton-employers-make-with-sponsor-licences</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Mock Audit with an Ex-Home Office Officer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>/resources-pages/mock-audit-with-an-ex-home-office-officer</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>6a99dd43b0fde4ff7a383280</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/mock-audit-with-an-ex-home-office-officer</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Prepare for a Home Office Immigration Compliance Audit</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>/resources-pages/prepare-for-a-home-office-immigration-compliance-audit</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>6a99dcf9a36cbb5c4112cf1c</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/prepare-for-a-home-office-immigration-compliance-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Pros and Cons of Sponsoring an Immigrant in the UK</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>/resources-pages/pros-and-cons-of-sponsoring-an-immigrant-in-uk</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>6a99dd3de99260a959f59ec2</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/pros-and-cons-of-sponsoring-an-immigrant-in-uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Right to Work Guidance - Supplementary Employment and Students</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>/resources-pages/right-to-work-guidance-supplementary-employment-students</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>6a99dd24cdae18d80850b62a</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/right-to-work-guidance-supplementary-employment-students</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Self-Sponsorship Visa UK</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>/resources-pages/self-sponsorship-visa-uk</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>6a99dd03c0cf7932055cf55f</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/self-sponsorship-visa-uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Settle in the UK - British Citizenship Through Naturalisation</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>/resources-pages/settle-in-the-uk--british-citizenship-through-naturalisation</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>6a99dd1927dcf5fe2105f425</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/settle-in-the-uk--british-citizenship-through-naturalisation</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Sponsor Licence Challenges Brighton HR Teams Face in 2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>/resources-pages/sponsor-licence-challenges-brighton-hr-teams-face-in-2025</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>6a99dd0683cc493fad26201a</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/sponsor-licence-challenges-brighton-hr-teams-face-in-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>How Much Does a Sponsor Licence Cost for SMEs in Brighton &amp; Sussex in 2026</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>/resources-pages/sponsor-licence-cost-for-smes-in-brighton-sussex</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>6a99dd42fda75d37369386ac</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/sponsor-licence-cost-for-smes-in-brighton-sussex</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>UK Spouse Visa Application Guide in 2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>/resources-pages/spouse-visa-uk-application-apply-for-partner-visa-in-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d4a3</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/spouse-visa-uk-application-apply-for-partner-visa-in-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Step-by-Step Guide to the UK Spouse Visa Application Process</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>/resources-pages/step-by-step-guide-to-the-uk-spouse-visa-application-process</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>6a99dd252b6d13b7e416527d</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/step-by-step-guide-to-the-uk-spouse-visa-application-process</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Switch From Ukraine Scheme to Skilled Worker Visa</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>/resources-pages/switch-from-ukraine-scheme-to-skilled-worker-visa</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d4a5</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/switch-from-ukraine-scheme-to-skilled-worker-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>The Biggest Problems Companies Face During a Sponsor Licence Application</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>/resources-pages/the-biggest-problems-companies-face-during-a-sponsor-licence-application</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>6a99dd284ed9993034aa51f1</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/the-biggest-problems-companies-face-during-a-sponsor-licence-application</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>The Challenges of Obtaining a CoS Allocation</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>/resources-pages/the-challenges-of-obtaining-a-cos-allocation</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>6a99dd0f9d5f41f647d331ff</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/the-challenges-of-obtaining-a-cos-allocation</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>The Hidden Risks of Not Preparing for a Home Office Compliance Visit</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>/resources-pages/the-hidden-risks-of-not-preparing-for-a-home-office-compliance-visit</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>6a99dd299f2eccd67839e096</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/the-hidden-risks-of-not-preparing-for-a-home-office-compliance-visit</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>The Most Trusted Sponsor Licence Advisers in the UK 2026 Guide</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>/resources-pages/the-most-trusted-sponsor-licence-advisers-in-the-uk-2025-guide</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>6a99dd3717c8e400a5f91fe7</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/the-most-trusted-sponsor-licence-advisers-in-the-uk-2025-guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>The Real Risk of Sponsoring Overseas Workers</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>/resources-pages/the-real-risk-of-sponsoring-overseas-workers-in-the-uk-and-how-to-avoid-fines</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>6a99dd3827dcf5fe210600f7</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/the-real-risk-of-sponsoring-overseas-workers-in-the-uk-and-how-to-avoid-fines</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>The UK Immigration Process - A Guide for Newcomers</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>/resources-pages/the-uk-immigration-process-a-guide-for-newcomers</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>6a99dcfa47e6b2f63825fee8</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/the-uk-immigration-process-a-guide-for-newcomers</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Top 10 Sponsor Licence Mistakes Employers Still Make in 2026</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>/resources-pages/top-10-sponsor-licence-mistakes-employers-still-make-in-2025</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>6a99dd00c681fe9cb0ad8daa</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/top-10-sponsor-licence-mistakes-employers-still-make-in-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Top 10 Tips for a Successful UK Visit Visa Application in 2026</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>/resources-pages/top-10-tips-for-a-successful-uk-visit-visa-application-in-2025</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>6a99dd439f2eccd67839eddb</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/top-10-tips-for-a-successful-uk-visit-visa-application-in-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Top 5 Best Immigration Consultants in the UK</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>/resources-pages/top-5-best-immigration-consultants-in-the-uk</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>6a99dd2af8cbaee8eba66ead</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/top-5-best-immigration-consultants-in-the-uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>UK Ancestry Visa</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-ancestry-visa</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d4a7</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-ancestry-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>UK Residency Self Sponsorship &amp; Expansion Worker Visas</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-business-residency-uk-self-sponsorship-and-expansion-worker-visas</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d4a9</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-business-residency-uk-self-sponsorship-and-expansion-worker-visas</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>UK Business Visitor Visa</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-business-visitor-visa</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>6a99dd102b6d13b7e4164510</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-business-visitor-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>UK Business Visitor Visa Applications</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-business-visitor-visa-a-guide-to-successful-applications</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d4ab</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-business-visitor-visa-a-guide-to-successful-applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>UK Citizenship: British Citizenship by Descent from a Grandparent</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-citizenship-british-citizenship-by-descent-from-a-grandparent</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d4ad</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-citizenship-british-citizenship-by-descent-from-a-grandparent</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>UK Civil Partner Visa</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-civil-partner-visa</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>6a99dd39d0b04e0ab977dc11</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-civil-partner-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>UK Construction Immigration - Visa Options for Employers</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-construction-immigration-visa-options</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d4af</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-construction-immigration-visa-options</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>5e. UK Creative Visitor Visa</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-creative-visitor-visa</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>6a99dd3632a470f0a32c89e0</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-creative-visitor-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>UK Dependent Visas</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-dependent-visas</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>6a99dd4439c5e9b9a9563196</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-dependent-visas</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>UK Dual Nationality and Multiple Citizenship</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-dual-nationality-and-multiple-citizenship</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>6a99dd26118257ad28e4bd8e</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-dual-nationality-and-multiple-citizenship</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>UK Expansion Worker Visa (GBM)</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-expansion-worker-visa-global-business-mobility-visa</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>6a99dd1158447882c71128a2</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-expansion-worker-visa-global-business-mobility-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>UK Family Visitor Visa</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-family-visitor-visa</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>6a99dd2aa64961b7c41d9951</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-family-visitor-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>UK Fiance Visa</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-fiance-visa</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>6a99dd3e118257ad28e4c74c</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-fiance-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>UK Global Talent Visa</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-global-talent-visa</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>6a99dd3f4c88ae31eb35c05b</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-global-talent-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>UK Graduate Visa</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-graduate-visa</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>6a99dd459ec6a6a97fde28cf</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-graduate-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>UK Health and Care Worker Visa</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-health-and-care-worker-visa</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d4b1</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-health-and-care-worker-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>UK Hospitality: Bridging Staff Shortages with Visa Options in 2025</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-hospitality-bridging-staff-shortages-with-visa-options</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d4b3</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-hospitality-bridging-staff-shortages-with-visa-options</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>UK India Young Professionals Scheme Visa</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-india-young-professionals-scheme-visa</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d4b5</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-india-young-professionals-scheme-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>UK Innovator Founder Visa</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-innovator-founder-visa</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>6a99dd4739c5e9b9a9563239</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-innovator-founder-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>UK International Sportsperson Visa (T2)</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-international-sportsperson-visa-t2</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d4b7</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-international-sportsperson-visa-t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>5b. UK Marriage Visitor Visa</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-marriage-visitor-visa</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>6a99dd332b6d13b7e416894b</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-marriage-visitor-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>5c. UK Medical Visitor Visa</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-medical-visitor-visa</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>6a99dd346002fe2f66ebc5d5</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-medical-visitor-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>UK Minister of Religion Visa (T2)</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-minister-of-religion-visa</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d4b9</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-minister-of-religion-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>UK Scale-up Visa</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-scale-up-visa</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>6a99dd01f848456aa81de0ba</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-scale-up-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>UK Secondment Worker Visa (GBM)</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-secondment-worker-visa-global-business-mobility-visa</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>6a99dd26e99260a959f592ca</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-secondment-worker-visa-global-business-mobility-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>UK Senior or Specialist Worker Visa (GBM)</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-senior-specialist-worker-visa-global-business-mobility-visa</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>6a99dcfb9d5f41f647d2f412</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-senior-specialist-worker-visa-global-business-mobility-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>UK Service Supplier Visa (GBM)</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-service-supplier-visa-global-business-mobility-visa</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>6a99dd2b17c8e400a5f91bc8</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-service-supplier-visa-global-business-mobility-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>UK Short-term Study Visa</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-short-term-study-visa</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>6a99dd3a9ec6a6a97fde237b</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-short-term-study-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>UK Skilled Worker Dependant Visa Process</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-skilled-worker-dependant-visa-process</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>6a99dd3bd0b04e0ab977dd0b</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-skilled-worker-dependant-visa-process</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>UK Skilled Worker Visa</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-skilled-worker-visa</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>6a99dcfd17c8e400a5f904d6</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-skilled-worker-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>5d. UK Sports Visitor Visa</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-sports-visitor-visa</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>6a99dd35c8b56b3f84121e8f</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-sports-visitor-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>UK Spouse and Partner Visa</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-spouse-and-partner-visa</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>6a99dd1bc7b865cc93b0d0ad</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-spouse-and-partner-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>6b. UK Student Visa</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-student-visa</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>6a99dd3b47e6b2f638261a00</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-student-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>UK Student Visa Application</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-student-visa-application-student-visa</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d4bb</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-student-visa-application-student-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>UK Charity Worker Visa</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-temporary-worker-charity-visa</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>6a99dd008c23868091cdfe85</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-temporary-worker-charity-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>UK Creative Worker Visa</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-temporary-worker-creative-visa</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>6a99dd04f56401e81197ea9d</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-temporary-worker-creative-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>UK Government Authorised Exchange Visa</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-temporary-worker-government-authorised-exchange-visa</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>6a99dd46a64961b7c41db765</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-temporary-worker-government-authorised-exchange-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>UK International Agreement Visa</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-temporary-worker-international-agreement-visa</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>6a99dd07c8b56b3f841209f4</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-temporary-worker-international-agreement-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>UK Religious Worker Visa Temporary Work</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-temporary-worker-religious-visa</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d4bd</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-temporary-worker-religious-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>UK Tourist Visa from India</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-tourist-visa-from-india</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>6a99dd3f0e9f3b3429d61445</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-tourist-visa-from-india</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>UK Tourist Visitor Visa</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-tourist-visitor-visa</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>6a99dcfecdae18d80850a871</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-tourist-visitor-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>UK Unmarried Partner Visa</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-unmarried-partner-visa</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>6a99dd2c4c88ae31eb35bb1b</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-unmarried-partner-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>UK Visa Invitation Letter Sample</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-visa-invitation-letter-sample</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>6a99dd2db3e9c79895ea47c6</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-visa-invitation-letter-sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>UK Visa Sponsorship in the UK Care Sector</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-visa-sponsorship-in-the-uk-care-sector</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d4bf</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-visa-sponsorship-in-the-uk-care-sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>UK Visa Tracking Guide: Stay Updated on Your Application Progress</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-visa-tracking-guide-stay-updated</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d4c1</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-visa-tracking-guide-stay-updated</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>UK Youth Mobility Visa - Work &amp; Travel</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>/resources-pages/uk-youth-mobility-scheme-visa</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>6aa14ee8cdf165fe7788d4c3</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/uk-youth-mobility-scheme-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>UKVI Majority English Speaking Countries</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>/resources-pages/ukvi-majority-english-speaking-countries</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>6a99dd1cc0cf7932055cfd81</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/ukvi-majority-english-speaking-countries</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Understanding Legal Responsibilities as a UK Sponsor Licence Holder</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>/resources-pages/understanding-legal-responsibilities-as-a-uk-sponsor-licence-holder</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>6a99dcfff38ff0e3e25a2fee</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/understanding-legal-responsibilities-as-a-uk-sponsor-licence-holder</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>What Activities Can a Business Visitor Undertake in the UK</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>/resources-pages/what-activities-can-a-business-visitor-undertake-in-the-uk</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>6a99dd1dfda75d37369376f1</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/what-activities-can-a-business-visitor-undertake-in-the-uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>What Does Having Indefinite Leave to Remain Mean</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>/resources-pages/what-does-having-indefinite-leave-to-remain-mean</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>6a99dd1247e6b2f638260c61</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/what-does-having-indefinite-leave-to-remain-mean</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>What Happens During a Home Office Compliance Audit</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>/resources-pages/what-happens-during-a-home-office-compliance-audit</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>6a99dd1d6002fe2f66ebb481</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/what-happens-during-a-home-office-compliance-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>What is the Skilled Worker Visa in the UK</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>/resources-pages/what-is-the-skilled-worker-visa-in-the-uk</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>6a99dd12b3e9c79895ea3f92</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/what-is-the-skilled-worker-visa-in-the-uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>What to Expect from a Home Office Pre-Licence Compliance Check</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>/resources-pages/what-to-expect-from-a-home-office-pre-licence-compliance-check</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>6a99dd132d7f345af543b0e7</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/what-to-expect-from-a-home-office-pre-licence-compliance-check</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Who Can Sponsor Me in the UK - Eligibility</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>/resources-pages/who-can-sponsor-me-in-the-uk--eligibility</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>6a99dd1e4c88ae31eb35a3d0</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/who-can-sponsor-me-in-the-uk--eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Why Are Skilled Worker Visa Applications Being Refused in 2026</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>/resources-pages/why-are-skilled-worker-visa-applications-being-refused-in-2025</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>6a99dd48c801b6e75a4f2062</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/why-are-skilled-worker-visa-applications-being-refused-in-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Why Right to Work Checks Alone Wont Keep You Compliant</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>/resources-pages/why-right-to-work-checks-alone-wont-keep-you-compliant</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>6a99dd40c966faec2cc23256</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/why-right-to-work-checks-alone-wont-keep-you-compliant</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Will the Home Office Exercise Discretion in My Citizenship Application</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>/resources-pages/will-the-home-office-exercise-discretion-when-applying-for-british-citizenship</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>6a99dd2e27dcf5fe2105fa98</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/resources-pages/will-the-home-office-exercise-discretion-when-applying-for-british-citizenship</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Adanna Okafor</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Testimonials</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>/testimonials/adanna-okafor</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>6a95fab1d6aba8a73c9a563b</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/testimonials/adanna-okafor</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Alicia Cedron</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Testimonials</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>/testimonials/alicia-cedron</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>6a95fbe53b0358282ac9abfe</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/testimonials/alicia-cedron</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Anbu Arasan</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Testimonials</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>/testimonials/anbu-arasan</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>6a95fbe53b0358282ac9abfc</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/testimonials/anbu-arasan</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Claire Thompson</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Testimonials</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>/testimonials/claire-thompson</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>6a95fbe53b0358282ac9abf6</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/testimonials/claire-thompson</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Damini Naidu</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Testimonials</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>/testimonials/damini-naidu</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>6a95fbe53b0358282ac9abf8</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/testimonials/damini-naidu</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>David Lin</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Testimonials</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>/testimonials/david-lin</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>6a95fce94fafce73918a6233</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/testimonials/david-lin</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Hannah</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Testimonials</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>/testimonials/hannah</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>6a95fbe53b0358282ac9abfa</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/testimonials/hannah</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>James Flint</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Testimonials</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>/testimonials/james-flint</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>6a95fbe53b0358282ac9abec</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/testimonials/james-flint</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Louise Garner</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Testimonials</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>/testimonials/louise-garner</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>6a95fbe53b0358282ac9abf2</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/testimonials/louise-garner</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Marcus Wright</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Testimonials</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>/testimonials/marcus-wright</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>6a95fbe53b0358282ac9abe6</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/testimonials/marcus-wright</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Matt O'Connell</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Testimonials</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>/testimonials/matt-oconnell</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>6a95fbe53b0358282ac9abf0</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/testimonials/matt-oconnell</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Natalia Petrova</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Testimonials</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>/testimonials/natalia-petrova</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>6a95fbe53b0358282ac9abea</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/testimonials/natalia-petrova</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Olivia Hart</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Testimonials</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>/testimonials/olivia-hart</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>6a95fbe53b0358282ac9abe8</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/testimonials/olivia-hart</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Rajiv Patel</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Testimonials</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>/testimonials/rajiv-patel</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>6a95fbe53b0358282ac9abf4</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/testimonials/rajiv-patel</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Richard Lee</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Testimonials</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>/testimonials/richard-lee</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>6a95fa83d173fff0ecd0ff31</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/testimonials/richard-lee</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Salma Bibi</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Testimonials</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>/testimonials/salma-bibi</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>6a95fbe53b0358282ac9abee</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>No page (template not published)</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/testimonials/salma-bibi</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Buyer &amp; Commercial</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Topics</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>/topics/buyer-commercial</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>6a99cc9b93d28b3a6a8fd16c</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/topics/buyer-commercial</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Certificates of Sponsorship</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Topics</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>/topics/certificates-of-sponsorship</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>6a89ad3e781841544c56ee36</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/topics/certificates-of-sponsorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Compliance &amp; Mock Audits</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Topics</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>/topics/compliance-mock-audits</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>6a89ad3e781841544c56ee32</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/topics/compliance-mock-audits</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Enforcement, Revocations &amp; Suspensions</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Topics</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>/topics/enforcement-revocations-suspensions</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>6a89ad3e781841544c56ee3c</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/topics/enforcement-revocations-suspensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Family Visas</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Topics</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>/topics/family-visas</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>6a89ad3e781841544c56ee42</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/topics/family-visas</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Topics</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>/topics/general</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>6a89ad3e781841544c56ee3e</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/topics/general</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Global Business Mobility</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Topics</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>/topics/global-business-mobility</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>6a89b85e53a1515f5e6e5527</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/topics/global-business-mobility</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Right to Work</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Topics</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>/topics/right-to-work</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>6a89ad3e781841544c56ee38</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/topics/right-to-work</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Settlement, ILR &amp; Citizenship</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Topics</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>/topics/settlement-ilr-citizenship</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>6a89ad3e781841544c56ee44</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/topics/settlement-ilr-citizenship</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Sponsor Duties</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Topics</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>/topics/sponsor-duties</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>6a89ad3e781841544c56ee3a</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/topics/sponsor-duties</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Sponsor Licence Applications</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Topics</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>/topics/sponsor-licence-applications</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>6a89ad3e781841544c56ee34</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/topics/sponsor-licence-applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Visitor &amp; Short-term</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Topics</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>/topics/visitor-short-term</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>6a89ad3e781841544c56ee46</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/topics/visitor-short-term</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Work &amp; Sponsored Routes</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Topics</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>/topics/work-sponsored-routes</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>6a89ad3e781841544c56ee40</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>https://immtell.webflow.io/topics/work-sponsored-routes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F238"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F238" r:id="rId237"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>